--- a/Result/profitability/6227.xlsx
+++ b/Result/profitability/6227.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>1.79625</v>
+        <v>2.0975</v>
       </c>
       <c r="N2" t="n">
-        <v>10.015</v>
+        <v>9.858750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>1.65875</v>
+        <v>1.855</v>
       </c>
       <c r="N3" t="n">
-        <v>10.21625</v>
+        <v>9.94875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4175</v>
+        <v>1.67</v>
       </c>
       <c r="N4" t="n">
-        <v>10.445</v>
+        <v>10.225</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.22625</v>
+        <v>1.74375</v>
       </c>
       <c r="N5" t="n">
-        <v>11.525</v>
+        <v>12.17375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.29625</v>
+        <v>1.38</v>
       </c>
       <c r="N6" t="n">
-        <v>12.87625</v>
+        <v>12.83</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9149999999999999</v>
+        <v>1.03875</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3575</v>
+        <v>13.07375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5975</v>
+        <v>0.7025</v>
       </c>
       <c r="N8" t="n">
-        <v>13.75625</v>
+        <v>13.59</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6227</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6990</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6351</v>
+      </c>
+      <c r="E75" t="n">
+        <v>640</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="G75" t="n">
+        <v>405</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>379</v>
+      </c>
+      <c r="K75" t="n">
+        <v>292</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.641249999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1269083969465649</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.310606060606061</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
